--- a/reports/equipment_catalog.xlsx
+++ b/reports/equipment_catalog.xlsx
@@ -54461,7 +54461,7 @@
       </c>
       <c r="E335" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_kasukabe_daisakusen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_kasukabe_daisakusen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54488,7 +54488,7 @@
       </c>
       <c r="E336" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_kasukabe_daisakusen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_kasukabe_daisakusen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54515,7 +54515,7 @@
       </c>
       <c r="E337" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_kasukabe_daisakusen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_kasukabe_daisakusen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54542,7 +54542,7 @@
       </c>
       <c r="E338" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_kasukabe_daisakusen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_kasukabe_daisakusen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54569,7 +54569,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_kasukabe_daisakusen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_kasukabe_daisakusen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54596,7 +54596,7 @@
       </c>
       <c r="E340" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54623,7 +54623,7 @@
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54650,7 +54650,7 @@
       </c>
       <c r="E342" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54677,7 +54677,7 @@
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54704,7 +54704,7 @@
       </c>
       <c r="E344" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54731,7 +54731,7 @@
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54758,7 +54758,7 @@
       </c>
       <c r="E346" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54785,7 +54785,7 @@
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54812,7 +54812,7 @@
       </c>
       <c r="E348" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai_nixi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai_nixi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54839,7 +54839,7 @@
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jingyanggang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jingyanggang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54866,7 +54866,7 @@
       </c>
       <c r="E350" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jingyanggang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jingyanggang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54893,7 +54893,7 @@
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wulongshan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wulongshan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54920,7 +54920,7 @@
       </c>
       <c r="E352" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wulongshan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wulongshan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54947,7 +54947,7 @@
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wulongshan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wulongshan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -54974,7 +54974,7 @@
       </c>
       <c r="E354" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wulongshan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wulongshan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55001,7 +55001,7 @@
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55028,7 +55028,7 @@
       </c>
       <c r="E356" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55055,7 +55055,7 @@
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55082,7 +55082,7 @@
       </c>
       <c r="E358" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55109,7 +55109,7 @@
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55136,7 +55136,7 @@
       </c>
       <c r="E360" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55163,7 +55163,7 @@
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55190,7 +55190,7 @@
       </c>
       <c r="E362" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55217,7 +55217,7 @@
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_wagangzhai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_wagangzhai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55244,7 +55244,7 @@
       </c>
       <c r="E364" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fugui_shanzhuang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fugui_shanzhuang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55271,7 +55271,7 @@
       </c>
       <c r="E365" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fugui_shanzhuang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fugui_shanzhuang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55298,7 +55298,7 @@
       </c>
       <c r="E366" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fugui_shanzhuang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fugui_shanzhuang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55325,7 +55325,7 @@
       </c>
       <c r="E367" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fugui_shanzhuang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fugui_shanzhuang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55352,7 +55352,7 @@
       </c>
       <c r="E368" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55379,7 +55379,7 @@
       </c>
       <c r="E369" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55406,7 +55406,7 @@
       </c>
       <c r="E370" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55433,7 +55433,7 @@
       </c>
       <c r="E371" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55460,7 +55460,7 @@
       </c>
       <c r="E372" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55487,7 +55487,7 @@
       </c>
       <c r="E373" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55514,7 +55514,7 @@
       </c>
       <c r="E374" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55541,7 +55541,7 @@
       </c>
       <c r="E375" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55568,7 +55568,7 @@
       </c>
       <c r="E376" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shizipo_heidian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shizipo_heidian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55595,7 +55595,7 @@
       </c>
       <c r="E377" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -55622,7 +55622,7 @@
       </c>
       <c r="E378" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -55649,7 +55649,7 @@
       </c>
       <c r="E379" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -55676,7 +55676,7 @@
       </c>
       <c r="E380" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -55703,7 +55703,7 @@
       </c>
       <c r="E381" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55730,7 +55730,7 @@
       </c>
       <c r="E382" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55757,7 +55757,7 @@
       </c>
       <c r="E383" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55784,7 +55784,7 @@
       </c>
       <c r="E384" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55811,7 +55811,7 @@
       </c>
       <c r="E385" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55838,7 +55838,7 @@
       </c>
       <c r="E386" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55865,7 +55865,7 @@
       </c>
       <c r="E387" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55892,7 +55892,7 @@
       </c>
       <c r="E388" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shanhaiguan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shanhaiguan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55919,7 +55919,7 @@
       </c>
       <c r="E389" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shiren_daochang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shiren_daochang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55946,7 +55946,7 @@
       </c>
       <c r="E390" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shiren_daochang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shiren_daochang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -55973,7 +55973,7 @@
       </c>
       <c r="E391" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shiren_daochang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shiren_daochang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56000,7 +56000,7 @@
       </c>
       <c r="E392" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shiren_daochang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shiren_daochang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56027,7 +56027,7 @@
       </c>
       <c r="E393" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shiren_daochang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shiren_daochang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56054,7 +56054,7 @@
       </c>
       <c r="E394" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shiren_daochang.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shiren_daochang.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56081,7 +56081,7 @@
       </c>
       <c r="E395" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguanshou_chuxian.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguanshou_chuxian.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56108,7 +56108,7 @@
       </c>
       <c r="E396" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguanshou_chuxian.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguanshou_chuxian.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56135,7 +56135,7 @@
       </c>
       <c r="E397" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguanshou_chuxian.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguanshou_chuxian.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56162,7 +56162,7 @@
       </c>
       <c r="E398" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguanshou_chuxian.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguanshou_chuxian.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56189,7 +56189,7 @@
       </c>
       <c r="E399" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biwu_zhaoqin.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biwu_zhaoqin.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56216,7 +56216,7 @@
       </c>
       <c r="E400" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biwu_zhaoqin.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biwu_zhaoqin.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56243,7 +56243,7 @@
       </c>
       <c r="E401" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biwu_zhaoqin.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biwu_zhaoqin.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56270,7 +56270,7 @@
       </c>
       <c r="E402" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biwu_zhaoqin.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biwu_zhaoqin.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56297,7 +56297,7 @@
       </c>
       <c r="E403" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biwu_zhaoqin.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biwu_zhaoqin.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56324,7 +56324,7 @@
       </c>
       <c r="E404" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56351,7 +56351,7 @@
       </c>
       <c r="E405" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56378,7 +56378,7 @@
       </c>
       <c r="E406" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56405,7 +56405,7 @@
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56432,7 +56432,7 @@
       </c>
       <c r="E408" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56459,7 +56459,7 @@
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56486,7 +56486,7 @@
       </c>
       <c r="E410" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_1.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_1.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56513,7 +56513,7 @@
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56540,7 +56540,7 @@
       </c>
       <c r="E412" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56567,7 +56567,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56594,7 +56594,7 @@
       </c>
       <c r="E414" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56621,7 +56621,7 @@
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56648,7 +56648,7 @@
       </c>
       <c r="E416" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56675,7 +56675,7 @@
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56702,7 +56702,7 @@
       </c>
       <c r="E418" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_tianpeng_dijiao_2.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_tianpeng_dijiao_2.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56729,7 +56729,7 @@
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguan_chuniao.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguan_chuniao.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56756,7 +56756,7 @@
       </c>
       <c r="E420" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguan_chuniao.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguan_chuniao.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56783,7 +56783,7 @@
       </c>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56810,7 +56810,7 @@
       </c>
       <c r="E422" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56837,7 +56837,7 @@
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56864,7 +56864,7 @@
       </c>
       <c r="E424" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiguan_chuniao.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -56891,7 +56891,7 @@
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_dongtian_fudi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_dongtian_fudi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56918,7 +56918,7 @@
       </c>
       <c r="E426" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_dongtian_fudi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_dongtian_fudi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56945,7 +56945,7 @@
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_dongtian_fudi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_dongtian_fudi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56972,7 +56972,7 @@
       </c>
       <c r="E428" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_dongtian_fudi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_dongtian_fudi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -56999,7 +56999,7 @@
       </c>
       <c r="E429" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_dongtian_fudi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_dongtian_fudi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57026,7 +57026,7 @@
       </c>
       <c r="E430" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_dongtian_fudi.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_dongtian_fudi.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57053,7 +57053,7 @@
       </c>
       <c r="E431" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57080,7 +57080,7 @@
       </c>
       <c r="E432" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -57107,7 +57107,7 @@
       </c>
       <c r="E433" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57134,7 +57134,7 @@
       </c>
       <c r="E434" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57161,7 +57161,7 @@
       </c>
       <c r="E435" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57188,7 +57188,7 @@
       </c>
       <c r="E436" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57215,7 +57215,7 @@
       </c>
       <c r="E437" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57242,7 +57242,7 @@
       </c>
       <c r="E438" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57269,7 +57269,7 @@
       </c>
       <c r="E439" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57296,7 +57296,7 @@
       </c>
       <c r="E440" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_jiufeng_feihuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_jiufeng_feihuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57323,7 +57323,7 @@
       </c>
       <c r="E441" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57350,7 +57350,7 @@
       </c>
       <c r="E442" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57377,7 +57377,7 @@
       </c>
       <c r="E443" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57404,7 +57404,7 @@
       </c>
       <c r="E444" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57431,7 +57431,7 @@
       </c>
       <c r="E445" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57458,7 +57458,7 @@
       </c>
       <c r="E446" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57485,7 +57485,7 @@
       </c>
       <c r="E447" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57512,7 +57512,7 @@
       </c>
       <c r="E448" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57539,7 +57539,7 @@
       </c>
       <c r="E449" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57566,7 +57566,7 @@
       </c>
       <c r="E450" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57593,7 +57593,7 @@
       </c>
       <c r="E451" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_taozi_fenban.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_taozi_fenban.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57620,7 +57620,7 @@
       </c>
       <c r="E452" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_simian_chuge.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_simian_chuge.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57647,7 +57647,7 @@
       </c>
       <c r="E453" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_simian_chuge.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_simian_chuge.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57674,7 +57674,7 @@
       </c>
       <c r="E454" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_simian_chuge.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_simian_chuge.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57701,7 +57701,7 @@
       </c>
       <c r="E455" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57728,7 +57728,7 @@
       </c>
       <c r="E456" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57755,7 +57755,7 @@
       </c>
       <c r="E457" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57782,7 +57782,7 @@
       </c>
       <c r="E458" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57809,7 +57809,7 @@
       </c>
       <c r="E459" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57836,7 +57836,7 @@
       </c>
       <c r="E460" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57863,7 +57863,7 @@
       </c>
       <c r="E461" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57890,7 +57890,7 @@
       </c>
       <c r="E462" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57917,7 +57917,7 @@
       </c>
       <c r="E463" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuiji_manzu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuiji_manzu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57944,7 +57944,7 @@
       </c>
       <c r="E464" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57971,7 +57971,7 @@
       </c>
       <c r="E465" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -57998,7 +57998,7 @@
       </c>
       <c r="E466" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58025,7 +58025,7 @@
       </c>
       <c r="E467" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58052,7 +58052,7 @@
       </c>
       <c r="E468" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58079,7 +58079,7 @@
       </c>
       <c r="E469" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58106,7 +58106,7 @@
       </c>
       <c r="E470" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58133,7 +58133,7 @@
       </c>
       <c r="E471" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58160,7 +58160,7 @@
       </c>
       <c r="E472" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_liangshanbo_zhuyingtai.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_liangshanbo_zhuyingtai.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58187,7 +58187,7 @@
       </c>
       <c r="E473" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58214,7 +58214,7 @@
       </c>
       <c r="E474" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58241,7 +58241,7 @@
       </c>
       <c r="E475" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58268,7 +58268,7 @@
       </c>
       <c r="E476" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58295,7 +58295,7 @@
       </c>
       <c r="E477" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58322,7 +58322,7 @@
       </c>
       <c r="E478" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58349,7 +58349,7 @@
       </c>
       <c r="E479" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58376,7 +58376,7 @@
       </c>
       <c r="E480" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_biyou_candeng.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_biyou_candeng.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58403,7 +58403,7 @@
       </c>
       <c r="E481" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_shier_xianyin.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_shier_xianyin.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58430,7 +58430,7 @@
       </c>
       <c r="E482" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58457,7 +58457,7 @@
       </c>
       <c r="E483" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58484,7 +58484,7 @@
       </c>
       <c r="E484" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58511,7 +58511,7 @@
       </c>
       <c r="E485" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58538,7 +58538,7 @@
       </c>
       <c r="E486" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58565,7 +58565,7 @@
       </c>
       <c r="E487" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58592,7 +58592,7 @@
       </c>
       <c r="E488" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58619,7 +58619,7 @@
       </c>
       <c r="E489" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58646,7 +58646,7 @@
       </c>
       <c r="E490" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58673,7 +58673,7 @@
       </c>
       <c r="E491" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -58700,7 +58700,7 @@
       </c>
       <c r="E492" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58727,7 +58727,7 @@
       </c>
       <c r="E493" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58754,7 +58754,7 @@
       </c>
       <c r="E494" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58781,7 +58781,7 @@
       </c>
       <c r="E495" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58808,7 +58808,7 @@
       </c>
       <c r="E496" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58835,7 +58835,7 @@
       </c>
       <c r="E497" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58862,7 +58862,7 @@
       </c>
       <c r="E498" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58889,7 +58889,7 @@
       </c>
       <c r="E499" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58916,7 +58916,7 @@
       </c>
       <c r="E500" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58943,7 +58943,7 @@
       </c>
       <c r="E501" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58970,7 +58970,7 @@
       </c>
       <c r="E502" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -58997,7 +58997,7 @@
       </c>
       <c r="E503" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59024,7 +59024,7 @@
       </c>
       <c r="E504" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59051,7 +59051,7 @@
       </c>
       <c r="E505" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_fengbang_tianmen.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_fengbang_tianmen.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59078,7 +59078,7 @@
       </c>
       <c r="E506" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59105,7 +59105,7 @@
       </c>
       <c r="E507" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59132,7 +59132,7 @@
       </c>
       <c r="E508" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59159,7 +59159,7 @@
       </c>
       <c r="E509" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59186,7 +59186,7 @@
       </c>
       <c r="E510" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59213,7 +59213,7 @@
       </c>
       <c r="E511" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59240,7 +59240,7 @@
       </c>
       <c r="E512" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59267,7 +59267,7 @@
       </c>
       <c r="E513" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59294,7 +59294,7 @@
       </c>
       <c r="E514" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59321,7 +59321,7 @@
       </c>
       <c r="E515" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59348,7 +59348,7 @@
       </c>
       <c r="E516" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59375,7 +59375,7 @@
       </c>
       <c r="E517" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59402,7 +59402,7 @@
       </c>
       <c r="E518" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59429,7 +59429,7 @@
       </c>
       <c r="E519" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59456,7 +59456,7 @@
       </c>
       <c r="E520" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59483,7 +59483,7 @@
       </c>
       <c r="E521" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59510,7 +59510,7 @@
       </c>
       <c r="E522" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59537,7 +59537,7 @@
       </c>
       <c r="E523" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59564,7 +59564,7 @@
       </c>
       <c r="E524" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_zhuolu_zhongyuan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_zhuolu_zhongyuan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59591,7 +59591,7 @@
       </c>
       <c r="E525" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59618,7 +59618,7 @@
       </c>
       <c r="E526" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59645,7 +59645,7 @@
       </c>
       <c r="E527" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59672,7 +59672,7 @@
       </c>
       <c r="E528" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59699,7 +59699,7 @@
       </c>
       <c r="E529" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59726,7 +59726,7 @@
       </c>
       <c r="E530" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59753,7 +59753,7 @@
       </c>
       <c r="E531" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59780,7 +59780,7 @@
       </c>
       <c r="E532" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59807,7 +59807,7 @@
       </c>
       <c r="E533" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_guandu_zhizhan.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_guandu_zhizhan.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59834,7 +59834,7 @@
       </c>
       <c r="E534" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59861,7 +59861,7 @@
       </c>
       <c r="E535" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload；data/forge_blueprints.yaml</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload；data/forge_blueprints.yaml</t>
         </is>
       </c>
     </row>
@@ -59888,7 +59888,7 @@
       </c>
       <c r="E536" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59915,7 +59915,7 @@
       </c>
       <c r="E537" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59942,7 +59942,7 @@
       </c>
       <c r="E538" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59969,7 +59969,7 @@
       </c>
       <c r="E539" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -59996,7 +59996,7 @@
       </c>
       <c r="E540" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60023,7 +60023,7 @@
       </c>
       <c r="E541" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60050,7 +60050,7 @@
       </c>
       <c r="E542" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60077,7 +60077,7 @@
       </c>
       <c r="E543" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60104,7 +60104,7 @@
       </c>
       <c r="E544" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60131,7 +60131,7 @@
       </c>
       <c r="E545" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60158,7 +60158,7 @@
       </c>
       <c r="E546" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60185,7 +60185,7 @@
       </c>
       <c r="E547" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60212,7 +60212,7 @@
       </c>
       <c r="E548" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60239,7 +60239,7 @@
       </c>
       <c r="E549" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60266,7 +60266,7 @@
       </c>
       <c r="E550" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60293,7 +60293,7 @@
       </c>
       <c r="E551" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60320,7 +60320,7 @@
       </c>
       <c r="E552" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60347,7 +60347,7 @@
       </c>
       <c r="E553" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60374,7 +60374,7 @@
       </c>
       <c r="E554" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60401,7 +60401,7 @@
       </c>
       <c r="E555" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60428,7 +60428,7 @@
       </c>
       <c r="E556" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60455,7 +60455,7 @@
       </c>
       <c r="E557" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60482,7 +60482,7 @@
       </c>
       <c r="E558" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60509,7 +60509,7 @@
       </c>
       <c r="E559" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60536,7 +60536,7 @@
       </c>
       <c r="E560" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60563,7 +60563,7 @@
       </c>
       <c r="E561" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60590,7 +60590,7 @@
       </c>
       <c r="E562" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_huashan_lunjian_advanced.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_huashan_lunjian_advanced.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60617,7 +60617,7 @@
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_sishui_huaxiong_chengwei.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_sishui_huaxiong_chengwei.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60644,7 +60644,7 @@
       </c>
       <c r="E564" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_sishui_huaxiong_chengwei.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_sishui_huaxiong_chengwei.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60671,7 +60671,7 @@
       </c>
       <c r="E565" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_sishui_huaxiong_chengwei.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_sishui_huaxiong_chengwei.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60698,7 +60698,7 @@
       </c>
       <c r="E566" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_sishui_huaxiong_chengwei.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_sishui_huaxiong_chengwei.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60725,7 +60725,7 @@
       </c>
       <c r="E567" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_hulao_qunying_zhan_lvbu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_hulao_qunying_zhan_lvbu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60752,7 +60752,7 @@
       </c>
       <c r="E568" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_hulao_qunying_zhan_lvbu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_hulao_qunying_zhan_lvbu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60779,7 +60779,7 @@
       </c>
       <c r="E569" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_hulao_qunying_zhan_lvbu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_hulao_qunying_zhan_lvbu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60806,7 +60806,7 @@
       </c>
       <c r="E570" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_hulao_qunying_zhan_lvbu.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_hulao_qunying_zhan_lvbu.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60833,7 +60833,7 @@
       </c>
       <c r="E571" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_baimenlou_mingyun_jueze.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_baimenlou_mingyun_jueze.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60860,7 +60860,7 @@
       </c>
       <c r="E572" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_baimenlou_mingyun_jueze.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_baimenlou_mingyun_jueze.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60887,7 +60887,7 @@
       </c>
       <c r="E573" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_baimenlou_mingyun_jueze.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_baimenlou_mingyun_jueze.effect_payload</t>
         </is>
       </c>
     </row>
@@ -60914,7 +60914,7 @@
       </c>
       <c r="E574" s="3" t="inlineStr">
         <is>
-          <t>data/item_templates.yaml:mission_chest_baimenlou_mingyun_jueze.effect_payload</t>
+          <t>data/item_templates.yaml:mission_chest_v3_baimenlou_mingyun_jueze.effect_payload</t>
         </is>
       </c>
     </row>
